--- a/data/trans_dic/P16A09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,47</t>
+          <t>1,81; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,02</t>
+          <t>1,03; 3,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,36</t>
+          <t>0,61; 2,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,88</t>
+          <t>1,5; 3,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,25</t>
+          <t>2,52; 5,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,21</t>
+          <t>3,82; 7,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,84</t>
+          <t>2,57; 5,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,15</t>
+          <t>5,1; 7,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,44</t>
+          <t>2,54; 4,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,57</t>
+          <t>2,73; 4,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,61</t>
+          <t>1,85; 3,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,41</t>
+          <t>3,51; 5,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,87</t>
+          <t>1,75; 3,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,52</t>
+          <t>1,51; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,55</t>
+          <t>0,85; 2,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,22</t>
+          <t>0,53; 2,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,19</t>
+          <t>3,44; 6,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,1</t>
+          <t>4,98; 8,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,2</t>
+          <t>2,79; 5,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,86</t>
+          <t>3,8; 5,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,65</t>
+          <t>2,95; 4,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,38</t>
+          <t>3,45; 5,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,48</t>
+          <t>2,04; 3,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,6</t>
+          <t>1,94; 3,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,07</t>
+          <t>1,51; 4,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,35</t>
+          <t>0,97; 3,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,07</t>
+          <t>1,01; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,85</t>
+          <t>1,0; 2,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,19</t>
+          <t>4,42; 8,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,39</t>
+          <t>3,39; 6,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,36</t>
+          <t>2,6; 5,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,42</t>
+          <t>1,43; 4,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,5</t>
+          <t>3,18; 5,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,5</t>
+          <t>2,4; 4,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,7</t>
+          <t>1,99; 3,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,29</t>
+          <t>1,61; 3,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,75</t>
+          <t>2,32; 4,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,39</t>
+          <t>1,25; 3,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,69</t>
+          <t>0,41; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,7</t>
+          <t>1,19; 2,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,36</t>
+          <t>4,15; 7,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,95</t>
+          <t>4,96; 8,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,93</t>
+          <t>2,5; 5,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,24</t>
+          <t>4,83; 8,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,6</t>
+          <t>3,75; 5,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,42</t>
+          <t>3,54; 5,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,07</t>
+          <t>1,61; 3,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,4</t>
+          <t>3,53; 5,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,54</t>
+          <t>2,39; 3,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,67</t>
+          <t>1,6; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,79</t>
+          <t>0,98; 1,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,29</t>
+          <t>1,31; 2,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,9</t>
+          <t>4,33; 5,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,63</t>
+          <t>5,0; 6,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,46</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,88</t>
+          <t>4,2; 5,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,48</t>
+          <t>3,55; 4,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,53</t>
+          <t>3,54; 4,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,01</t>
+          <t>2,2; 3,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,92</t>
+          <t>2,99; 3,98</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13284; 31008</t>
+          <t>12517; 29759</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6381; 21181</t>
+          <t>7200; 22255</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3979; 15901</t>
+          <t>4105; 15481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9280; 24652</t>
+          <t>9549; 24679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17462; 36151</t>
+          <t>17322; 36897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25719; 49907</t>
+          <t>26453; 50429</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17724; 39296</t>
+          <t>17287; 38182</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33759; 55069</t>
+          <t>34444; 52640</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35930; 61383</t>
+          <t>35148; 59810</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37187; 63648</t>
+          <t>38011; 64768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24093; 48707</t>
+          <t>24971; 49259</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45894; 70918</t>
+          <t>45947; 71062</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16721; 37209</t>
+          <t>16858; 37649</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16061; 35859</t>
+          <t>15369; 35242</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9242; 26082</t>
+          <t>8711; 24751</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7617; 26504</t>
+          <t>6291; 26079</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32311; 59988</t>
+          <t>33357; 61109</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51567; 83276</t>
+          <t>51156; 82820</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28097; 54233</t>
+          <t>29090; 56728</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36653; 56130</t>
+          <t>36395; 56422</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55845; 89801</t>
+          <t>56945; 91344</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72537; 110119</t>
+          <t>70514; 109780</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41184; 71814</t>
+          <t>42068; 71571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41547; 77499</t>
+          <t>41750; 77065</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10604; 27636</t>
+          <t>10220; 27538</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7266; 25365</t>
+          <t>7315; 25612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7925; 23325</t>
+          <t>7675; 21756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6536; 20052</t>
+          <t>7057; 20114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30646; 56008</t>
+          <t>30256; 55210</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25893; 49580</t>
+          <t>26280; 49584</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19475; 42050</t>
+          <t>20430; 42296</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13484; 41157</t>
+          <t>13370; 42205</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46110; 74876</t>
+          <t>43358; 74974</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37980; 68941</t>
+          <t>36856; 67541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30996; 57078</t>
+          <t>30689; 58595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25128; 53798</t>
+          <t>26371; 54154</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23458; 44767</t>
+          <t>21884; 43951</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11753; 32035</t>
+          <t>11777; 32172</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3470; 15882</t>
+          <t>3808; 15665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10290; 24966</t>
+          <t>10984; 25770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44911; 76426</t>
+          <t>43109; 74936</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50314; 83341</t>
+          <t>52030; 85645</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26273; 51448</t>
+          <t>26129; 52653</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53768; 89959</t>
+          <t>52725; 88221</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73171; 110930</t>
+          <t>74362; 110706</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69715; 108033</t>
+          <t>70500; 109531</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32650; 60888</t>
+          <t>31907; 61288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71695; 109028</t>
+          <t>71120; 108913</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77076; 115878</t>
+          <t>78300; 114764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55242; 91401</t>
+          <t>54702; 90999</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34225; 60827</t>
+          <t>33114; 59638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45805; 79269</t>
+          <t>45136; 78273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>147850; 199364</t>
+          <t>146473; 198455</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>181182; 235216</t>
+          <t>177098; 236451</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>110223; 158235</t>
+          <t>111719; 159042</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>152825; 215091</t>
+          <t>153628; 214832</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>235279; 298426</t>
+          <t>236178; 301417</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>245081; 315223</t>
+          <t>246216; 313136</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154896; 209063</t>
+          <t>152690; 209726</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>211225; 278841</t>
+          <t>212623; 282968</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Habitat-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,29</t>
+          <t>1,83; 4,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,18</t>
+          <t>0,94; 3,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,29</t>
+          <t>0,62; 2,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,89</t>
+          <t>1,49; 3,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,36</t>
+          <t>2,59; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,28</t>
+          <t>3,82; 7,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,67</t>
+          <t>2,54; 5,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,79</t>
+          <t>5,18; 8,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,33</t>
+          <t>2,48; 4,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,65</t>
+          <t>2,64; 4,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,66</t>
+          <t>1,89; 3,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,42</t>
+          <t>3,6; 5,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,91</t>
+          <t>1,75; 3,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,46</t>
+          <t>1,57; 3,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,42</t>
+          <t>0,9; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,19</t>
+          <t>1,1; 2,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,31</t>
+          <t>3,28; 6,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,06</t>
+          <t>5,02; 8,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,44</t>
+          <t>2,77; 5,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,89</t>
+          <t>3,85; 5,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,73</t>
+          <t>2,87; 4,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,37</t>
+          <t>3,47; 5,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,47</t>
+          <t>2,07; 3,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,58</t>
+          <t>2,68; 3,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,06</t>
+          <t>1,51; 4,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,39</t>
+          <t>1,0; 3,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,86</t>
+          <t>0,95; 2,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,86</t>
+          <t>0,9; 2,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,07</t>
+          <t>4,41; 8,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,39</t>
+          <t>3,33; 6,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,39</t>
+          <t>2,61; 5,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,53</t>
+          <t>2,98; 5,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,5</t>
+          <t>3,33; 5,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,41</t>
+          <t>2,48; 4,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,79</t>
+          <t>2,02; 3,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,31</t>
+          <t>2,16; 3,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,66</t>
+          <t>2,36; 4,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,41</t>
+          <t>1,4; 3,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,67</t>
+          <t>0,41; 1,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,78</t>
+          <t>1,25; 2,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,21</t>
+          <t>4,32; 7,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,17</t>
+          <t>5,0; 8,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,04</t>
+          <t>2,49; 5,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,08</t>
+          <t>5,38; 7,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,59</t>
+          <t>3,68; 5,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,5</t>
+          <t>3,48; 5,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,09</t>
+          <t>1,68; 3,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,4</t>
+          <t>3,61; 5,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,5</t>
+          <t>2,4; 3,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,66</t>
+          <t>1,65; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,76</t>
+          <t>0,97; 1,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,26</t>
+          <t>1,49; 2,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,87</t>
+          <t>4,35; 5,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,67</t>
+          <t>5,04; 6,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,49</t>
+          <t>3,11; 4,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,87</t>
+          <t>4,89; 6,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,53</t>
+          <t>3,54; 4,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,5</t>
+          <t>3,55; 4,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,02</t>
+          <t>2,23; 2,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,98</t>
+          <t>3,35; 4,08</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42454</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57845</t>
+          <t>64019</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12517; 29759</t>
+          <t>12657; 30490</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7200; 22255</t>
+          <t>6555; 21525</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4105; 15481</t>
+          <t>4212; 15982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9549; 24679</t>
+          <t>10255; 26521</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17322; 36897</t>
+          <t>17814; 37169</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26453; 50429</t>
+          <t>26417; 52186</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17287; 38182</t>
+          <t>17090; 39658</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34444; 52640</t>
+          <t>37974; 59762</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35148; 59810</t>
+          <t>34191; 60678</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38011; 64768</t>
+          <t>36745; 65158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24971; 49259</t>
+          <t>25470; 48558</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45947; 71062</t>
+          <t>51220; 79023</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>69338</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16858; 37649</t>
+          <t>16845; 37218</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15369; 35242</t>
+          <t>16030; 35394</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8711; 24751</t>
+          <t>9223; 26451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6291; 26079</t>
+          <t>11571; 28688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33357; 61109</t>
+          <t>31783; 59566</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51156; 82820</t>
+          <t>51612; 83490</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29090; 56728</t>
+          <t>28868; 55901</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36395; 56422</t>
+          <t>41188; 62896</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56945; 91344</t>
+          <t>55438; 87852</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70514; 109780</t>
+          <t>71006; 108744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42068; 71571</t>
+          <t>42729; 72127</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41750; 77065</t>
+          <t>56800; 84632</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28759</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>45420</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10220; 27538</t>
+          <t>10279; 27596</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7315; 25612</t>
+          <t>7603; 25387</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7675; 21756</t>
+          <t>7215; 21376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7057; 20114</t>
+          <t>7201; 21546</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30256; 55210</t>
+          <t>30186; 54839</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26280; 49584</t>
+          <t>25815; 49545</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20430; 42296</t>
+          <t>20460; 43172</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13370; 42205</t>
+          <t>24150; 42144</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>43358; 74974</t>
+          <t>45408; 73202</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36856; 67541</t>
+          <t>37962; 68312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30689; 58595</t>
+          <t>31174; 58530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26371; 54154</t>
+          <t>34874; 57166</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16982</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>69682</t>
+          <t>72161</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86664</t>
+          <t>90758</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21884; 43951</t>
+          <t>22197; 43205</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11777; 32172</t>
+          <t>13251; 33586</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3808; 15665</t>
+          <t>3823; 16116</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10984; 25770</t>
+          <t>12373; 28029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43109; 74936</t>
+          <t>44896; 76299</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52030; 85645</t>
+          <t>52490; 84432</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26129; 52653</t>
+          <t>25978; 52451</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52725; 88221</t>
+          <t>60071; 87350</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74362; 110706</t>
+          <t>72964; 111552</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70500; 109531</t>
+          <t>69425; 110420</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31907; 61288</t>
+          <t>33354; 61563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71120; 108913</t>
+          <t>76035; 108439</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>203735</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>246942</t>
+          <t>269535</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>78300; 114764</t>
+          <t>78523; 115374</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54702; 90999</t>
+          <t>56285; 91026</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33114; 59638</t>
+          <t>33086; 60175</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45136; 78273</t>
+          <t>52578; 83495</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>146473; 198455</t>
+          <t>147081; 200905</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>177098; 236451</t>
+          <t>178549; 236700</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>111719; 159042</t>
+          <t>110235; 158867</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>153628; 214832</t>
+          <t>182405; 226977</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>236178; 301417</t>
+          <t>235431; 299774</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>246216; 313136</t>
+          <t>247370; 309906</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152690; 209726</t>
+          <t>154872; 206987</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>212623; 282968</t>
+          <t>242954; 296333</t>
         </is>
       </c>
     </row>
